--- a/main/ig/mappingConsentementCDAFHIR.xlsx
+++ b/main/ig/mappingConsentementCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T15:44:19+00:00</t>
+    <t>2025-08-01T08:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingConsentementCDAFHIR.xlsx
+++ b/main/ig/mappingConsentementCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-01T08:11:50+00:00</t>
+    <t>2025-08-22T10:16:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingConsentementCDAFHIR.xlsx
+++ b/main/ig/mappingConsentementCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T10:16:53+00:00</t>
+    <t>2025-08-25T15:42:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingConsentementCDAFHIR.xlsx
+++ b/main/ig/mappingConsentementCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T15:42:10+00:00</t>
+    <t>2025-10-02T14:05:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingConsentementCDAFHIR.xlsx
+++ b/main/ig/mappingConsentementCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T14:05:03+00:00</t>
+    <t>2025-10-02T15:16:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingConsentementCDAFHIR.xlsx
+++ b/main/ig/mappingConsentementCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T15:16:38+00:00</t>
+    <t>2025-10-13T15:21:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingConsentementCDAFHIR.xlsx
+++ b/main/ig/mappingConsentementCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-13T15:21:05+00:00</t>
+    <t>2025-10-20T17:15:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingConsentementCDAFHIR.xlsx
+++ b/main/ig/mappingConsentementCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-20T17:15:49+00:00</t>
+    <t>2025-10-21T08:14:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingConsentementCDAFHIR.xlsx
+++ b/main/ig/mappingConsentementCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T08:14:34+00:00</t>
+    <t>2025-10-21T15:23:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingConsentementCDAFHIR.xlsx
+++ b/main/ig/mappingConsentementCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T15:23:03+00:00</t>
+    <t>2025-10-21T16:49:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -105,16 +105,16 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/Consentement</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-consentement</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-authorization</t>
-  </si>
-  <si>
-    <t>Consentement</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-authorization</t>
+  </si>
+  <si>
+    <t>FRLMConsentement</t>
   </si>
   <si>
     <t>equivalent</t>
@@ -123,19 +123,19 @@
     <t>authorization</t>
   </si>
   <si>
-    <t>Consentement.identifiantConsentement</t>
+    <t>FRLMConsentement.identifiantConsentement</t>
   </si>
   <si>
     <t>authorization.consent.id</t>
   </si>
   <si>
-    <t>Consentement.typeConsentement</t>
+    <t>FRLMConsentement.typeConsentement</t>
   </si>
   <si>
     <t>authorization.consent.code</t>
   </si>
   <si>
-    <t>Consentement.statutConsentement</t>
+    <t>FRLMConsentement.statutConsentement</t>
   </si>
   <si>
     <t>authorization.consent.statusCode="completed"</t>

--- a/main/ig/mappingConsentementCDAFHIR.xlsx
+++ b/main/ig/mappingConsentementCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T16:49:23+00:00</t>
+    <t>2025-10-21T17:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingConsentementCDAFHIR.xlsx
+++ b/main/ig/mappingConsentementCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T17:18:21+00:00</t>
+    <t>2025-10-22T08:56:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
